--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.626296088914434</v>
+        <v>0.9142731144485956</v>
       </c>
       <c r="D2" t="n">
-        <v>25.31290574637586</v>
+        <v>4.113347183786078</v>
       </c>
       <c r="E2" t="n">
-        <v>11.17779998738284</v>
+        <v>1.816392497949711</v>
       </c>
       <c r="F2" t="n">
-        <v>6.599451997664366</v>
+        <v>1.072410949620459</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.5213863420266</v>
+        <v>3.822225280579322</v>
       </c>
       <c r="D3" t="n">
-        <v>24.72245117032223</v>
+        <v>4.017398315177362</v>
       </c>
       <c r="E3" t="n">
-        <v>11.17779998738284</v>
+        <v>1.816392497949711</v>
       </c>
       <c r="F3" t="n">
-        <v>6.599451997664366</v>
+        <v>1.072410949620459</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.910660419340704</v>
+        <v>1.285482318142864</v>
       </c>
       <c r="D4" t="n">
-        <v>21.92207656177289</v>
+        <v>3.562337441288095</v>
       </c>
       <c r="E4" t="n">
-        <v>11.17779998738284</v>
+        <v>1.816392497949711</v>
       </c>
       <c r="F4" t="n">
-        <v>6.599451997664366</v>
+        <v>1.072410949620459</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.62320785223488</v>
+        <v>1.888771275988167</v>
       </c>
       <c r="D5" t="n">
-        <v>10.71861685533496</v>
+        <v>1.741775238991931</v>
       </c>
       <c r="E5" t="n">
-        <v>11.17779998738284</v>
+        <v>1.816392497949711</v>
       </c>
       <c r="F5" t="n">
-        <v>6.599451997664366</v>
+        <v>1.072410949620459</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.522816151845001</v>
+        <v>1.547457624674813</v>
       </c>
       <c r="D6" t="n">
-        <v>10.44038077475745</v>
+        <v>1.696561875898086</v>
       </c>
       <c r="E6" t="n">
-        <v>11.17779998738284</v>
+        <v>1.816392497949711</v>
       </c>
       <c r="F6" t="n">
-        <v>6.599451997664366</v>
+        <v>1.072410949620459</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.82448723564046</v>
+        <v>4.033979175791575</v>
       </c>
       <c r="D7" t="n">
-        <v>24.51780314115934</v>
+        <v>3.984143010438393</v>
       </c>
       <c r="E7" t="n">
-        <v>11.17779998738284</v>
+        <v>1.816392497949711</v>
       </c>
       <c r="F7" t="n">
-        <v>6.599451997664366</v>
+        <v>1.072410949620459</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.73197230472383</v>
+        <v>4.018945499517621</v>
       </c>
       <c r="D8" t="n">
-        <v>24.1915364707393</v>
+        <v>3.931124676495136</v>
       </c>
       <c r="E8" t="n">
-        <v>11.17779998738284</v>
+        <v>1.816392497949711</v>
       </c>
       <c r="F8" t="n">
-        <v>6.599451997664366</v>
+        <v>1.072410949620459</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.31124187153745</v>
+        <v>3.625576804124835</v>
       </c>
       <c r="D9" t="n">
-        <v>22.70842780237169</v>
+        <v>3.6901195178854</v>
       </c>
       <c r="E9" t="n">
-        <v>11.17779998738284</v>
+        <v>1.816392497949711</v>
       </c>
       <c r="F9" t="n">
-        <v>6.599451997664366</v>
+        <v>1.072410949620459</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.20628432910587</v>
+        <v>3.121021203479704</v>
       </c>
       <c r="D10" t="n">
-        <v>19.16438617946151</v>
+        <v>3.114212754162495</v>
       </c>
       <c r="E10" t="n">
-        <v>11.17779998738284</v>
+        <v>1.816392497949711</v>
       </c>
       <c r="F10" t="n">
-        <v>6.599451997664366</v>
+        <v>1.072410949620459</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>13.88391681325355</v>
+        <v>2.256136482153702</v>
       </c>
       <c r="D11" t="n">
-        <v>14.26326134103319</v>
+        <v>2.317779967917894</v>
       </c>
       <c r="E11" t="n">
-        <v>11.17779998738284</v>
+        <v>1.816392497949711</v>
       </c>
       <c r="F11" t="n">
-        <v>6.599451997664366</v>
+        <v>1.072410949620459</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>47.35696391203334</v>
+        <v>7.695506635705419</v>
       </c>
       <c r="D12" t="n">
-        <v>6.168971581549727</v>
+        <v>1.002457882001831</v>
       </c>
       <c r="E12" t="n">
-        <v>11.17779998738284</v>
+        <v>1.816392497949711</v>
       </c>
       <c r="F12" t="n">
-        <v>6.599451997664366</v>
+        <v>1.072410949620459</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
